--- a/docs/detail-design/12_BangGia.xlsx
+++ b/docs/detail-design/12_BangGia.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="151">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · SỬA BẢNG GIÁ</t>
   </si>
@@ -134,6 +134,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Tên cột "{N} giờ đầu" đổi ngay theo số giờ tối thiểu đang nhập; ô thiếu tô đỏ + hộp lỗi khi lưu; giới hạn độ dài tên hạng.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Dialog Sửa bảng giá</t>
   </si>
   <si>
@@ -203,7 +209,7 @@
     <t>Dưới ô: các số phòng đang dùng hạng.</t>
   </si>
   <si>
-    <t>2 giờ đầu</t>
+    <t>{N} giờ đầu</t>
   </si>
   <si>
     <t>Ô nhập số (đ)</t>
@@ -218,7 +224,7 @@
     <t>≥ 0.</t>
   </si>
   <si>
-    <t>Giá cho số giờ tối thiểu đầu tiên.</t>
+    <t>Giá cho số giờ tối thiểu đầu tiên. Tên cột "{N} giờ đầu" đổi ngay khi sửa ô số giờ tối thiểu (minHours()).</t>
   </si>
   <si>
     <t>Mỗi giờ thêm</t>
@@ -305,7 +311,7 @@
     <t>≥ 1.</t>
   </si>
   <si>
-    <t>Đơn theo giờ phải thuê ≥ số giờ này; tên cột "2 giờ đầu" ở tab Bảng giá đổi theo số này.</t>
+    <t>Đơn theo giờ phải thuê ≥ số giờ này. Gợi ý dưới ô: "Cột giá "… giờ đầu" đổi theo số này" — tên cột giá giờ đầu trong dialog, tab Bảng giá, thẻ phòng, màn Thêm/Sửa phòng đều theo số này.</t>
   </si>
   <si>
     <t>Qua đêm: giờ nhận → giờ trả hôm sau</t>
@@ -371,7 +377,7 @@
     <t>2. Lưu — PUT /api/room-types/overview</t>
   </si>
   <si>
-    <t>Frontend: ô trống / giá âm / số giờ tối thiểu &lt; 1 → không gửi (không tô đỏ ô).</t>
+    <t>Frontend: ô trống / giá âm / số giờ tối thiểu &lt; 1 → tô đỏ ô, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", không gửi. Tên hạng tối đa 100 ký tự (maxlength).</t>
   </si>
   <si>
     <t>2.</t>
@@ -438,6 +444,21 @@
   </si>
   <si>
     <t>Hạng phòng không tồn tại</t>
+  </si>
+  <si>
+    <t>Thiếu ô / giá âm / số giờ tối thiểu &lt; 1</t>
+  </si>
+  <si>
+    <t>frontend</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đủ các ô bắt buộc (viền đỏ).</t>
+  </si>
+  <si>
+    <t>Tên hạng quá 100 ký tự (gọi thẳng API)</t>
+  </si>
+  <si>
+    <t>Dữ liệu không hợp lệ — errors["roomTypes[i].name"]: "Tối đa 100 ký tự"</t>
   </si>
   <si>
     <t>Nhân viên gọi API</t>
@@ -993,7 +1014,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1724,8 +1745,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1765,6 +1828,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1784,7 +1851,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1820,7 +1887,7 @@
     </row>
     <row r="46" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -1878,7 +1945,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1914,10 +1981,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -1928,22 +1995,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -1951,12 +2018,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -1969,33 +2036,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2003,12 +2070,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2021,33 +2088,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2055,12 +2122,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2068,38 +2135,38 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="5" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2107,12 +2174,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2125,33 +2192,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2159,12 +2226,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2177,33 +2244,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2211,12 +2278,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2229,33 +2296,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2263,12 +2330,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2281,33 +2348,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2315,12 +2382,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2333,33 +2400,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2367,12 +2434,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2385,33 +2452,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2419,12 +2486,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2437,33 +2504,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2471,12 +2538,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2484,38 +2551,38 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
     </row>
-    <row r="13" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="13" ht="95" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2523,12 +2590,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2541,33 +2608,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2575,12 +2642,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2593,33 +2660,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2627,12 +2694,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2645,33 +2712,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -2679,12 +2746,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2694,7 +2761,7 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -2730,10 +2797,10 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2744,22 +2811,22 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2767,12 +2834,12 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
@@ -2785,33 +2852,33 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -2819,12 +2886,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2982,7 +3049,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG20"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2991,7 +3058,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3027,7 +3094,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3063,10 +3130,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3101,7 +3168,7 @@
     </row>
     <row r="5" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3135,12 +3202,12 @@
       <c r="AF5" s="4"/>
       <c r="AG5" s="4"/>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="6" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -3175,10 +3242,10 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -3213,10 +3280,10 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -3251,10 +3318,10 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -3289,10 +3356,10 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -3327,10 +3394,10 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -3365,7 +3432,7 @@
     </row>
     <row r="13" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -3401,7 +3468,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -3415,11 +3482,11 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
@@ -3441,7 +3508,7 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -3459,7 +3526,7 @@
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -3481,7 +3548,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -3499,7 +3566,7 @@
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -3521,7 +3588,7 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -3539,7 +3606,7 @@
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -3561,7 +3628,7 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3579,7 +3646,7 @@
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -3601,7 +3668,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -3614,12 +3681,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="6">
-        <v>403</v>
-      </c>
-      <c r="O19" s="6"/>
+      <c r="N19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -3641,7 +3708,7 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -3654,12 +3721,12 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O20" s="3"/>
+      <c r="N20" s="6">
+        <v>400</v>
+      </c>
+      <c r="O20" s="6"/>
       <c r="P20" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -3679,8 +3746,88 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="6">
+        <v>403</v>
+      </c>
+      <c r="O21" s="6"/>
+      <c r="P21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="38">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="C3:AG3"/>
@@ -3713,6 +3860,12 @@
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:AG20"/>
+    <mergeCell ref="B21:M21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:AG21"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
